--- a/Spark/Data/Simulated/Bruno/model_run/results/ranking_importancia_VS_cost_sp_persist.xlsx
+++ b/Spark/Data/Simulated/Bruno/model_run/results/ranking_importancia_VS_cost_sp_persist.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t xml:space="preserve">term</t>
   </si>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">Mean degree — periphery</t>
   </si>
   <si>
-    <t xml:space="preserve">β=0.47***</t>
+    <t xml:space="preserve">β=0.46***</t>
   </si>
   <si>
     <t xml:space="preserve">Cp = 0.1</t>
@@ -159,9 +159,6 @@
   </si>
   <si>
     <t xml:space="preserve">β=0.24***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">β=-0.31***</t>
   </si>
   <si>
     <t xml:space="preserve">β=-0.32***</t>
@@ -536,16 +533,16 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.121591635178494</v>
+        <v>-0.121767583603067</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.217421743446031</v>
+        <v>-0.217568447774766</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0257615269109564</v>
+        <v>-0.0259667194313682</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0128879269060882</v>
+        <v>0.0127308820383669</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -568,16 +565,16 @@
         <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.0302996079333454</v>
+        <v>-0.0307735485929124</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.153798740895793</v>
+        <v>-0.154234761812622</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0931995250291021</v>
+        <v>0.092687664626797</v>
       </c>
       <c r="E3" t="n">
-        <v>0.630614005020846</v>
+        <v>0.6251713818529</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -600,16 +597,16 @@
         <v>19</v>
       </c>
       <c r="B4" t="n">
-        <v>0.32176460087138</v>
+        <v>0.321854346130516</v>
       </c>
       <c r="C4" t="n">
-        <v>0.192159856189458</v>
+        <v>0.192289161488102</v>
       </c>
       <c r="D4" t="n">
-        <v>0.451369345553302</v>
+        <v>0.451419530772929</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00000113922441125069</v>
+        <v>0.00000112295704801646</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
@@ -632,13 +629,13 @@
         <v>23</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.357549093679766</v>
+        <v>-0.357380436167433</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.443638155082906</v>
+        <v>-0.443443001251103</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.271460032276627</v>
+        <v>-0.271317871083763</v>
       </c>
       <c r="E5" t="n">
         <v>0.000000000000000444089209850063</v>
@@ -664,16 +661,16 @@
         <v>26</v>
       </c>
       <c r="B6" t="n">
-        <v>0.506093927069936</v>
+        <v>0.506098316453499</v>
       </c>
       <c r="C6" t="n">
-        <v>0.363998215782288</v>
+        <v>0.364046152120192</v>
       </c>
       <c r="D6" t="n">
-        <v>0.648189638357584</v>
+        <v>0.648150480786805</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00000000000293742807855324</v>
+        <v>0.00000000000289168688993868</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -696,13 +693,13 @@
         <v>29</v>
       </c>
       <c r="B7" t="n">
-        <v>0.465163613955702</v>
+        <v>0.4649413186598</v>
       </c>
       <c r="C7" t="n">
-        <v>0.384449484696155</v>
+        <v>0.384251975979485</v>
       </c>
       <c r="D7" t="n">
-        <v>0.545877743215249</v>
+        <v>0.545630661340116</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -728,16 +725,16 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.0197604269733348</v>
+        <v>-0.0198975728678462</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.115471952590707</v>
+        <v>-0.115579823974424</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0759510986440378</v>
+        <v>0.0757846782387311</v>
       </c>
       <c r="E8" t="n">
-        <v>0.685734367200321</v>
+        <v>0.683579331092715</v>
       </c>
       <c r="F8" t="s">
         <v>32</v>
@@ -760,16 +757,16 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0699015678825966</v>
+        <v>-0.0703773400047988</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1933270026286</v>
+        <v>-0.19376483467087</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0535238668634067</v>
+        <v>0.0530101546612727</v>
       </c>
       <c r="E9" t="n">
-        <v>0.266990916452588</v>
+        <v>0.263602188043822</v>
       </c>
       <c r="F9" t="s">
         <v>32</v>
@@ -792,16 +789,16 @@
         <v>19</v>
       </c>
       <c r="B10" t="n">
-        <v>0.170301157460192</v>
+        <v>0.170417886798133</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0408081350265559</v>
+        <v>0.0409644467935745</v>
       </c>
       <c r="D10" t="n">
-        <v>0.299794179893828</v>
+        <v>0.299871326802692</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00994825974928548</v>
+        <v>0.00987493950889884</v>
       </c>
       <c r="F10" t="s">
         <v>32</v>
@@ -824,16 +821,16 @@
         <v>23</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.333538115268038</v>
+        <v>-0.333345061493098</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.419616521562368</v>
+        <v>-0.419396968657494</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.247459708973709</v>
+        <v>-0.247293154328703</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0000000000000308642000845794</v>
+        <v>0.0000000000000313082892944294</v>
       </c>
       <c r="F11" t="s">
         <v>32</v>
@@ -856,16 +853,16 @@
         <v>26</v>
       </c>
       <c r="B12" t="n">
-        <v>0.434467717618965</v>
+        <v>0.434441065778933</v>
       </c>
       <c r="C12" t="n">
-        <v>0.292406255219343</v>
+        <v>0.292423160393732</v>
       </c>
       <c r="D12" t="n">
-        <v>0.576529180018587</v>
+        <v>0.576458971164134</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00000000204522709879029</v>
+        <v>0.00000000202680250360743</v>
       </c>
       <c r="F12" t="s">
         <v>32</v>
@@ -888,13 +885,13 @@
         <v>29</v>
       </c>
       <c r="B13" t="n">
-        <v>0.407674038512257</v>
+        <v>0.407466514718843</v>
       </c>
       <c r="C13" t="n">
-        <v>0.327032261058893</v>
+        <v>0.326849542999538</v>
       </c>
       <c r="D13" t="n">
-        <v>0.488315815965622</v>
+        <v>0.488083486438147</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -920,16 +917,16 @@
         <v>10</v>
       </c>
       <c r="B14" t="n">
-        <v>0.139620854810137</v>
+        <v>0.13949905971855</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0440398749265221</v>
+        <v>0.0439474007423602</v>
       </c>
       <c r="D14" t="n">
-        <v>0.235201834693752</v>
+        <v>0.235050718694739</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00419602046135559</v>
+        <v>0.00421752036449519</v>
       </c>
       <c r="F14" t="s">
         <v>40</v>
@@ -952,16 +949,16 @@
         <v>15</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.218130411454016</v>
+        <v>-0.218580058943784</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.341462450890763</v>
+        <v>-0.341874127289232</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0947983720172686</v>
+        <v>-0.0952859905983355</v>
       </c>
       <c r="E15" t="n">
-        <v>0.000527325698556957</v>
+        <v>0.000511438195747393</v>
       </c>
       <c r="F15" t="s">
         <v>40</v>
@@ -984,16 +981,16 @@
         <v>19</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.137645134645165</v>
+        <v>-0.137556095665544</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.267033719625239</v>
+        <v>-0.266905058949363</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.00825654966509087</v>
+        <v>-0.00820713238172557</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0370662791718344</v>
+        <v>0.0371308147582836</v>
       </c>
       <c r="F16" t="s">
         <v>40</v>
@@ -1016,16 +1013,16 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.273842776773571</v>
+        <v>-0.27365245079824</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.359908808601094</v>
+        <v>-0.35969197919098</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.187776744946049</v>
+        <v>-0.1876129224055</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000000000448427961430298</v>
+        <v>0.000000000455398385668104</v>
       </c>
       <c r="F17" t="s">
         <v>40</v>
@@ -1048,16 +1045,16 @@
         <v>26</v>
       </c>
       <c r="B18" t="n">
-        <v>0.256085499972229</v>
+        <v>0.256065813751479</v>
       </c>
       <c r="C18" t="n">
-        <v>0.114065686932229</v>
+        <v>0.114089571803163</v>
       </c>
       <c r="D18" t="n">
-        <v>0.398105313012228</v>
+        <v>0.398042055699794</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0004090993632484</v>
+        <v>0.000407843017411036</v>
       </c>
       <c r="F18" t="s">
         <v>40</v>
@@ -1080,13 +1077,13 @@
         <v>29</v>
       </c>
       <c r="B19" t="n">
-        <v>0.3983236826486</v>
+        <v>0.398113402180916</v>
       </c>
       <c r="C19" t="n">
-        <v>0.317728516519812</v>
+        <v>0.317543059503893</v>
       </c>
       <c r="D19" t="n">
-        <v>0.478918848777388</v>
+        <v>0.478683744857938</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1112,16 +1109,16 @@
         <v>10</v>
       </c>
       <c r="B20" t="n">
-        <v>0.236758053800317</v>
+        <v>0.236588280630994</v>
       </c>
       <c r="C20" t="n">
-        <v>0.141192692933834</v>
+        <v>0.14105224275568</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3323234146668</v>
+        <v>0.332124318506308</v>
       </c>
       <c r="E20" t="n">
-        <v>0.00000119958810707033</v>
+        <v>0.00000121171061651104</v>
       </c>
       <c r="F20" t="s">
         <v>47</v>
@@ -1144,16 +1141,16 @@
         <v>15</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.314505879406494</v>
+        <v>-0.315010289322265</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.43782734299079</v>
+        <v>-0.438293778551864</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.191184415822198</v>
+        <v>-0.191726800092665</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000000577832036663395</v>
+        <v>0.000000549867001264914</v>
       </c>
       <c r="F21" t="s">
         <v>47</v>
@@ -1176,16 +1173,16 @@
         <v>19</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.316592764052907</v>
+        <v>-0.316495500576056</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.445970139630266</v>
+        <v>-0.445833252378249</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.187215388475548</v>
+        <v>-0.187157748773864</v>
       </c>
       <c r="E22" t="n">
-        <v>0.00000161762175654445</v>
+        <v>0.00000161765871409258</v>
       </c>
       <c r="F22" t="s">
         <v>47</v>
@@ -1200,7 +1197,7 @@
         <v>21</v>
       </c>
       <c r="J22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
@@ -1208,16 +1205,16 @@
         <v>23</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.240167239927664</v>
+        <v>-0.239971711161643</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.326231800647438</v>
+        <v>-0.326009767709454</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.154102679207891</v>
+        <v>-0.153933654613832</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0000000451631705367106</v>
+        <v>0.0000000458741513664762</v>
       </c>
       <c r="F23" t="s">
         <v>47</v>
@@ -1232,7 +1229,7 @@
         <v>24</v>
       </c>
       <c r="J23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
@@ -1240,16 +1237,16 @@
         <v>26</v>
       </c>
       <c r="B24" t="n">
-        <v>0.159413412948353</v>
+        <v>0.159371053371817</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0173989081855057</v>
+        <v>0.0174001213180737</v>
       </c>
       <c r="D24" t="n">
-        <v>0.301427917711201</v>
+        <v>0.30134198542556</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0278005820356479</v>
+        <v>0.0277941669149788</v>
       </c>
       <c r="F24" t="s">
         <v>47</v>
@@ -1264,7 +1261,7 @@
         <v>27</v>
       </c>
       <c r="J24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25">
@@ -1272,13 +1269,13 @@
         <v>29</v>
       </c>
       <c r="B25" t="n">
-        <v>0.413735374028413</v>
+        <v>0.413524439915392</v>
       </c>
       <c r="C25" t="n">
-        <v>0.333145935828746</v>
+        <v>0.332959826765719</v>
       </c>
       <c r="D25" t="n">
-        <v>0.494324812228079</v>
+        <v>0.494089053065066</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
